--- a/thaco/color/1_DATA_AllCols.xlsx
+++ b/thaco/color/1_DATA_AllCols.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adity/Documents/GitHub/gitlocal/thaco/color/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAA1DF04-DCF1-C943-B5FC-3162BBEB758E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E76ED5A-EF50-D142-8565-9DC0BEBB74FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39360" yWindow="860" windowWidth="33760" windowHeight="18480" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="41300" yWindow="500" windowWidth="33760" windowHeight="18480" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bảng lương CB-NV" sheetId="5" r:id="rId1"/>
@@ -6191,7 +6191,7 @@
         <v>48</v>
       </c>
       <c r="F8" s="26">
-        <v>6340000</v>
+        <v>9000010</v>
       </c>
       <c r="G8" s="25">
         <v>1</v>

--- a/thaco/color/1_DATA_AllCols.xlsx
+++ b/thaco/color/1_DATA_AllCols.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adity/Documents/GitHub/gitlocal/thaco/color/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E76ED5A-EF50-D142-8565-9DC0BEBB74FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F4CED3E-1BAA-D249-B120-629CCCE188B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="41300" yWindow="500" windowWidth="33760" windowHeight="18480" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="39220" yWindow="600" windowWidth="33760" windowHeight="18480" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bảng lương CB-NV" sheetId="5" r:id="rId1"/>
@@ -4339,7 +4339,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="71">
   <si>
     <t>MSNV</t>
   </si>
@@ -4524,9 +4524,6 @@
     <t>Nguyễn Ngọc Thủy Tiên</t>
   </si>
   <si>
-    <t>ĐP PCCC</t>
-  </si>
-  <si>
     <t>Nguyễn Hồng Nhung</t>
   </si>
   <si>
@@ -4549,6 +4546,12 @@
   </si>
   <si>
     <t>Realization part 1</t>
+  </si>
+  <si>
+    <t>Fire prevention team</t>
+  </si>
+  <si>
+    <t>Fire Department</t>
   </si>
 </sst>
 </file>
@@ -4561,7 +4564,7 @@
     <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4686,6 +4689,12 @@
     <font>
       <i/>
       <sz val="11"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -4818,7 +4827,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4985,6 +4994,9 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="9">
@@ -5388,7 +5400,8 @@
     <col min="31" max="41" width="10.5" style="51" customWidth="1"/>
     <col min="42" max="42" width="12.5" style="51" customWidth="1"/>
     <col min="43" max="46" width="12.6640625" style="51" customWidth="1" outlineLevel="1"/>
-    <col min="47" max="48" width="10.6640625" style="54" customWidth="1" outlineLevel="1"/>
+    <col min="47" max="47" width="16.5" style="54" bestFit="1" customWidth="1" outlineLevel="1"/>
+    <col min="48" max="48" width="10.6640625" style="54" customWidth="1" outlineLevel="1"/>
     <col min="49" max="49" width="19.5" style="55" customWidth="1"/>
     <col min="50" max="50" width="12.33203125" style="55" customWidth="1"/>
     <col min="51" max="51" width="12.5" style="55" customWidth="1"/>
@@ -5521,7 +5534,7 @@
         <v>32</v>
       </c>
       <c r="AP1" s="64" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AQ1" s="65" t="s">
         <v>14</v>
@@ -5550,7 +5563,7 @@
         <v>55</v>
       </c>
       <c r="C2" s="35" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D2" s="36" t="s">
         <v>47</v>
@@ -5643,7 +5656,9 @@
       <c r="AT2" s="39">
         <v>200000</v>
       </c>
-      <c r="AU2" s="39"/>
+      <c r="AU2" s="69" t="s">
+        <v>69</v>
+      </c>
       <c r="AV2" s="39"/>
     </row>
     <row r="3" spans="1:53" s="1" customFormat="1" ht="14" customHeight="1" outlineLevel="1">
@@ -5654,7 +5669,7 @@
         <v>56</v>
       </c>
       <c r="C3" s="35" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D3" s="36" t="s">
         <v>47</v>
@@ -5747,7 +5762,9 @@
       <c r="AT3" s="39">
         <v>200000</v>
       </c>
-      <c r="AU3" s="39"/>
+      <c r="AU3" s="69" t="s">
+        <v>70</v>
+      </c>
       <c r="AV3" s="39"/>
     </row>
     <row r="4" spans="1:53" s="1" customFormat="1" ht="14" customHeight="1" outlineLevel="1">
@@ -5758,7 +5775,7 @@
         <v>57</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D4" s="36" t="s">
         <v>47</v>
@@ -5851,7 +5868,9 @@
       <c r="AT4" s="39">
         <v>200000</v>
       </c>
-      <c r="AU4" s="39"/>
+      <c r="AU4" s="69" t="s">
+        <v>54</v>
+      </c>
       <c r="AV4" s="39"/>
     </row>
     <row r="5" spans="1:53" s="28" customFormat="1" ht="19.25" customHeight="1">
@@ -5862,7 +5881,7 @@
         <v>58</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D5" s="36" t="s">
         <v>47</v>
@@ -5955,7 +5974,9 @@
       <c r="AT5" s="39">
         <v>200000</v>
       </c>
-      <c r="AU5" s="39"/>
+      <c r="AU5" s="69" t="s">
+        <v>70</v>
+      </c>
       <c r="AV5" s="39"/>
       <c r="AZ5" s="29"/>
       <c r="BA5" s="30"/>
@@ -5968,7 +5989,7 @@
         <v>59</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D6" s="36" t="s">
         <v>47</v>
@@ -6061,7 +6082,9 @@
       <c r="AT6" s="39">
         <v>200000</v>
       </c>
-      <c r="AU6" s="39"/>
+      <c r="AU6" s="69" t="s">
+        <v>54</v>
+      </c>
       <c r="AV6" s="39"/>
       <c r="AZ6" s="29"/>
       <c r="BA6" s="30"/>
@@ -6074,7 +6097,7 @@
         <v>60</v>
       </c>
       <c r="C7" s="35" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D7" s="36" t="s">
         <v>52</v>
@@ -6167,8 +6190,8 @@
       <c r="AT7" s="39">
         <v>200000</v>
       </c>
-      <c r="AU7" s="39" t="s">
-        <v>61</v>
+      <c r="AU7" s="69" t="s">
+        <v>70</v>
       </c>
       <c r="AV7" s="39"/>
       <c r="AZ7" s="29"/>
@@ -6179,10 +6202,10 @@
         <v>53</v>
       </c>
       <c r="B8" s="34" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D8" s="36" t="s">
         <v>47</v>
@@ -6275,7 +6298,7 @@
       <c r="AT8" s="39">
         <v>200000</v>
       </c>
-      <c r="AU8" s="39" t="s">
+      <c r="AU8" s="69" t="s">
         <v>54</v>
       </c>
       <c r="AV8" s="39"/>
@@ -6378,7 +6401,7 @@
       <c r="AJ10" s="14"/>
       <c r="AK10" s="14"/>
       <c r="AL10" s="14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AM10" s="14"/>
       <c r="AN10" s="14"/>

--- a/thaco/color/1_DATA_AllCols.xlsx
+++ b/thaco/color/1_DATA_AllCols.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adity/Documents/GitHub/gitlocal/thaco/color/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{421B0ED1-BF6C-034D-9B1E-AD7D64BF4169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A487890-4523-BC49-8FCE-1106C5FF6D92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="39220" yWindow="600" windowWidth="33760" windowHeight="18480" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4167,7 +4167,7 @@
     <author>tc={F2CA1CEE-0407-4ECA-B543-A94DFE1E09BB}</author>
   </authors>
   <commentList>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{7F1822B3-CF41-9C4C-AF6A-101E0D0CD369}">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{7F1822B3-CF41-9C4C-AF6A-101E0D0CD369}">
       <text>
         <r>
           <rPr>
@@ -4240,7 +4240,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="1" shapeId="0" xr:uid="{894EFCB7-ADAC-6A40-AF91-4567D0ABDEB0}">
+    <comment ref="F1" authorId="1" shapeId="0" xr:uid="{894EFCB7-ADAC-6A40-AF91-4567D0ABDEB0}">
       <text>
         <r>
           <rPr>
@@ -4339,7 +4339,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="72">
   <si>
     <t>MSNV</t>
   </si>
@@ -4552,6 +4552,9 @@
   </si>
   <si>
     <t>Fire Department</t>
+  </si>
+  <si>
+    <t>TT</t>
   </si>
 </sst>
 </file>
@@ -4827,7 +4830,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4997,6 +5000,15 @@
     </xf>
     <xf numFmtId="164" fontId="22" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="9">
@@ -5384,205 +5396,209 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:BA18"/>
+  <dimension ref="A1:BB18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" outlineLevelRow="1" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="8.5" style="47" customWidth="1"/>
-    <col min="2" max="2" width="15.83203125" style="56" customWidth="1"/>
-    <col min="3" max="3" width="15.83203125" style="49" customWidth="1" outlineLevel="1"/>
-    <col min="4" max="4" width="8.5" style="49" bestFit="1" customWidth="1" outlineLevel="1"/>
-    <col min="5" max="5" width="11.5" style="50" customWidth="1" outlineLevel="1"/>
-    <col min="6" max="6" width="13.6640625" style="51" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.5" style="52" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="21" width="7.1640625" style="53" customWidth="1"/>
-    <col min="22" max="29" width="12.33203125" style="51" customWidth="1"/>
-    <col min="30" max="30" width="13" style="51" customWidth="1"/>
-    <col min="31" max="41" width="10.5" style="51" customWidth="1"/>
-    <col min="42" max="42" width="12.5" style="51" customWidth="1"/>
-    <col min="43" max="46" width="12.6640625" style="51" customWidth="1" outlineLevel="1"/>
-    <col min="47" max="47" width="16.5" style="54" bestFit="1" customWidth="1" outlineLevel="1"/>
-    <col min="48" max="48" width="10.6640625" style="54" customWidth="1" outlineLevel="1"/>
-    <col min="49" max="49" width="19.5" style="55" customWidth="1"/>
-    <col min="50" max="50" width="12.33203125" style="55" customWidth="1"/>
-    <col min="51" max="51" width="12.5" style="55" customWidth="1"/>
-    <col min="52" max="52" width="11.6640625" style="55" customWidth="1"/>
-    <col min="53" max="16384" width="9.1640625" style="55"/>
+    <col min="1" max="1" width="9.1640625" style="55"/>
+    <col min="2" max="2" width="8.5" style="47" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" style="56" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" style="49" customWidth="1" outlineLevel="1"/>
+    <col min="5" max="5" width="8.5" style="49" bestFit="1" customWidth="1" outlineLevel="1"/>
+    <col min="6" max="6" width="11.5" style="50" customWidth="1" outlineLevel="1"/>
+    <col min="7" max="7" width="13.6640625" style="51" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.5" style="52" customWidth="1" outlineLevel="1"/>
+    <col min="9" max="22" width="7.1640625" style="53" customWidth="1"/>
+    <col min="23" max="30" width="12.33203125" style="51" customWidth="1"/>
+    <col min="31" max="31" width="13" style="51" customWidth="1"/>
+    <col min="32" max="42" width="10.5" style="51" customWidth="1"/>
+    <col min="43" max="43" width="12.5" style="51" customWidth="1"/>
+    <col min="44" max="47" width="12.6640625" style="51" customWidth="1" outlineLevel="1"/>
+    <col min="48" max="48" width="16.5" style="54" bestFit="1" customWidth="1" outlineLevel="1"/>
+    <col min="49" max="49" width="10.6640625" style="54" customWidth="1" outlineLevel="1"/>
+    <col min="50" max="50" width="19.5" style="55" customWidth="1"/>
+    <col min="51" max="51" width="12.33203125" style="55" customWidth="1"/>
+    <col min="52" max="52" width="12.5" style="55" customWidth="1"/>
+    <col min="53" max="53" width="11.6640625" style="55" customWidth="1"/>
+    <col min="54" max="16384" width="9.1640625" style="55"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53" s="68" customFormat="1" ht="54" customHeight="1" outlineLevel="1">
-      <c r="A1" s="57" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="58" t="s">
+    <row r="1" spans="1:54" s="68" customFormat="1" ht="54" customHeight="1" outlineLevel="1">
+      <c r="A1" s="72" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1" s="57" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="59" t="s">
+      <c r="D1" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="59" t="s">
+      <c r="E1" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="58" t="s">
+      <c r="F1" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="58" t="s">
+      <c r="G1" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="58" t="s">
+      <c r="H1" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="60" t="s">
+      <c r="I1" s="60" t="s">
         <v>17</v>
       </c>
-      <c r="I1" s="60" t="s">
+      <c r="J1" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="J1" s="60" t="s">
+      <c r="K1" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="K1" s="60" t="s">
+      <c r="L1" s="60" t="s">
         <v>20</v>
       </c>
-      <c r="L1" s="60" t="s">
+      <c r="M1" s="60" t="s">
         <v>21</v>
       </c>
-      <c r="M1" s="60" t="s">
+      <c r="N1" s="60" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="60" t="s">
+      <c r="O1" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="O1" s="60" t="s">
+      <c r="P1" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="P1" s="60" t="s">
+      <c r="Q1" s="60" t="s">
         <v>25</v>
       </c>
-      <c r="Q1" s="60" t="s">
+      <c r="R1" s="60" t="s">
         <v>26</v>
       </c>
-      <c r="R1" s="60" t="s">
+      <c r="S1" s="60" t="s">
         <v>27</v>
       </c>
-      <c r="S1" s="61" t="s">
+      <c r="T1" s="61" t="s">
         <v>42</v>
       </c>
-      <c r="T1" s="61" t="s">
+      <c r="U1" s="61" t="s">
         <v>43</v>
       </c>
-      <c r="U1" s="60" t="s">
+      <c r="V1" s="60" t="s">
         <v>28</v>
       </c>
-      <c r="V1" s="58" t="s">
+      <c r="W1" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="W1" s="58" t="s">
+      <c r="X1" s="58" t="s">
         <v>30</v>
       </c>
-      <c r="X1" s="58" t="s">
+      <c r="Y1" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="Y1" s="58" t="s">
+      <c r="Z1" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="Z1" s="58" t="s">
+      <c r="AA1" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="AA1" s="58" t="s">
+      <c r="AB1" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="AB1" s="58" t="s">
+      <c r="AC1" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="AC1" s="58" t="s">
+      <c r="AD1" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="AD1" s="58" t="s">
+      <c r="AE1" s="58" t="s">
         <v>13</v>
       </c>
-      <c r="AE1" s="62" t="s">
+      <c r="AF1" s="62" t="s">
         <v>33</v>
       </c>
-      <c r="AF1" s="62" t="s">
+      <c r="AG1" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="AG1" s="62" t="s">
+      <c r="AH1" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="AH1" s="62" t="s">
+      <c r="AI1" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="AI1" s="62" t="s">
+      <c r="AJ1" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="AJ1" s="58" t="s">
+      <c r="AK1" s="58" t="s">
         <v>38</v>
       </c>
-      <c r="AK1" s="62" t="s">
+      <c r="AL1" s="62" t="s">
         <v>39</v>
       </c>
-      <c r="AL1" s="58" t="s">
+      <c r="AM1" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="AM1" s="58" t="s">
+      <c r="AN1" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="AN1" s="63" t="s">
+      <c r="AO1" s="63" t="s">
         <v>31</v>
       </c>
-      <c r="AO1" s="63" t="s">
+      <c r="AP1" s="63" t="s">
         <v>32</v>
       </c>
-      <c r="AP1" s="64" t="s">
+      <c r="AQ1" s="64" t="s">
         <v>68</v>
       </c>
-      <c r="AQ1" s="65" t="s">
+      <c r="AR1" s="65" t="s">
         <v>14</v>
       </c>
-      <c r="AR1" s="66" t="s">
+      <c r="AS1" s="66" t="s">
         <v>44</v>
       </c>
-      <c r="AS1" s="66" t="s">
+      <c r="AT1" s="66" t="s">
         <v>45</v>
       </c>
-      <c r="AT1" s="66" t="s">
+      <c r="AU1" s="66" t="s">
         <v>46</v>
       </c>
-      <c r="AU1" s="67" t="s">
+      <c r="AV1" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="AV1" s="67" t="s">
+      <c r="AW1" s="67" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:53" s="1" customFormat="1" ht="14" customHeight="1" outlineLevel="1">
-      <c r="A2" s="33">
+    <row r="2" spans="1:54" s="1" customFormat="1" ht="14" customHeight="1" outlineLevel="1">
+      <c r="A2" s="71">
+        <v>1</v>
+      </c>
+      <c r="B2" s="33">
         <v>2405236</v>
       </c>
-      <c r="B2" s="34" t="s">
+      <c r="C2" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="C2" s="35" t="s">
+      <c r="D2" s="35" t="s">
         <v>63</v>
       </c>
-      <c r="D2" s="36" t="s">
+      <c r="E2" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="E2" s="36" t="s">
+      <c r="F2" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="F2" s="26">
+      <c r="G2" s="26">
         <v>9520000</v>
       </c>
-      <c r="G2" s="25">
+      <c r="H2" s="25">
         <v>1</v>
       </c>
-      <c r="H2" s="37">
+      <c r="I2" s="37">
         <v>26</v>
       </c>
-      <c r="I2" s="37">
-        <v>0</v>
-      </c>
       <c r="J2" s="37">
         <v>0</v>
       </c>
@@ -5604,10 +5620,10 @@
       <c r="P2" s="37">
         <v>0</v>
       </c>
-      <c r="Q2" s="37"/>
-      <c r="R2" s="37">
-        <v>0</v>
-      </c>
+      <c r="Q2" s="37">
+        <v>0</v>
+      </c>
+      <c r="R2" s="37"/>
       <c r="S2" s="37">
         <v>0</v>
       </c>
@@ -5617,81 +5633,84 @@
       <c r="U2" s="37">
         <v>0</v>
       </c>
-      <c r="V2" s="26"/>
+      <c r="V2" s="37">
+        <v>0</v>
+      </c>
       <c r="W2" s="26"/>
       <c r="X2" s="26"/>
       <c r="Y2" s="26"/>
-      <c r="Z2" s="26">
+      <c r="Z2" s="26"/>
+      <c r="AA2" s="26">
         <v>1000000</v>
       </c>
-      <c r="AA2" s="26"/>
       <c r="AB2" s="26"/>
       <c r="AC2" s="26"/>
       <c r="AD2" s="26"/>
-      <c r="AE2" s="38"/>
+      <c r="AE2" s="26"/>
       <c r="AF2" s="38"/>
-      <c r="AG2" s="38">
+      <c r="AG2" s="38"/>
+      <c r="AH2" s="38">
         <v>3</v>
       </c>
-      <c r="AH2" s="38">
+      <c r="AI2" s="38">
         <v>6200000</v>
       </c>
-      <c r="AI2" s="38"/>
       <c r="AJ2" s="38"/>
-      <c r="AK2" s="38">
-        <v>0</v>
-      </c>
-      <c r="AL2" s="38"/>
+      <c r="AK2" s="38"/>
+      <c r="AL2" s="38">
+        <v>0</v>
+      </c>
       <c r="AM2" s="38"/>
       <c r="AN2" s="38"/>
       <c r="AO2" s="38"/>
-      <c r="AP2" s="51"/>
-      <c r="AQ2" s="40">
+      <c r="AP2" s="38"/>
+      <c r="AQ2" s="51"/>
+      <c r="AR2" s="40">
         <v>60000000</v>
       </c>
-      <c r="AR2" s="39">
-        <v>0</v>
-      </c>
-      <c r="AS2" s="39"/>
-      <c r="AT2" s="39">
+      <c r="AS2" s="39">
+        <v>0</v>
+      </c>
+      <c r="AT2" s="39"/>
+      <c r="AU2" s="39">
         <v>200000</v>
       </c>
-      <c r="AU2" s="69" t="s">
+      <c r="AV2" s="69" t="s">
         <v>69</v>
       </c>
-      <c r="AV2" s="39"/>
+      <c r="AW2" s="39"/>
     </row>
-    <row r="3" spans="1:53" s="1" customFormat="1" ht="14" customHeight="1" outlineLevel="1">
-      <c r="A3" s="33">
+    <row r="3" spans="1:54" s="1" customFormat="1" ht="14" customHeight="1" outlineLevel="1">
+      <c r="A3" s="70">
+        <v>2</v>
+      </c>
+      <c r="B3" s="33">
         <v>2106723</v>
       </c>
-      <c r="B3" s="34" t="s">
+      <c r="C3" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="C3" s="35" t="s">
+      <c r="D3" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="D3" s="36" t="s">
+      <c r="E3" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="E3" s="36" t="s">
+      <c r="F3" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="26">
+      <c r="G3" s="26">
         <v>8480000</v>
       </c>
-      <c r="G3" s="25">
+      <c r="H3" s="25">
         <v>1</v>
       </c>
-      <c r="H3" s="37">
+      <c r="I3" s="37">
         <v>19</v>
       </c>
-      <c r="I3" s="37">
+      <c r="J3" s="37">
         <v>5</v>
       </c>
-      <c r="J3" s="37">
-        <v>0</v>
-      </c>
       <c r="K3" s="37">
         <v>0</v>
       </c>
@@ -5710,10 +5729,10 @@
       <c r="P3" s="37">
         <v>0</v>
       </c>
-      <c r="Q3" s="37"/>
-      <c r="R3" s="37">
-        <v>0</v>
-      </c>
+      <c r="Q3" s="37">
+        <v>0</v>
+      </c>
+      <c r="R3" s="37"/>
       <c r="S3" s="37">
         <v>0</v>
       </c>
@@ -5723,78 +5742,81 @@
       <c r="U3" s="37">
         <v>0</v>
       </c>
-      <c r="V3" s="26"/>
+      <c r="V3" s="37">
+        <v>0</v>
+      </c>
       <c r="W3" s="26"/>
       <c r="X3" s="26"/>
       <c r="Y3" s="26"/>
-      <c r="Z3" s="26">
+      <c r="Z3" s="26"/>
+      <c r="AA3" s="26">
         <v>720000</v>
       </c>
-      <c r="AA3" s="26"/>
       <c r="AB3" s="26"/>
       <c r="AC3" s="26"/>
       <c r="AD3" s="26"/>
-      <c r="AE3" s="38"/>
+      <c r="AE3" s="26"/>
       <c r="AF3" s="38"/>
       <c r="AG3" s="38"/>
-      <c r="AH3" s="38">
+      <c r="AH3" s="38"/>
+      <c r="AI3" s="38">
         <v>6200000</v>
       </c>
-      <c r="AI3" s="38"/>
       <c r="AJ3" s="38"/>
-      <c r="AK3" s="38">
-        <v>0</v>
-      </c>
-      <c r="AL3" s="38"/>
+      <c r="AK3" s="38"/>
+      <c r="AL3" s="38">
+        <v>0</v>
+      </c>
       <c r="AM3" s="38"/>
       <c r="AN3" s="38"/>
       <c r="AO3" s="38"/>
-      <c r="AP3" s="51"/>
-      <c r="AQ3" s="40">
+      <c r="AP3" s="38"/>
+      <c r="AQ3" s="51"/>
+      <c r="AR3" s="40">
         <v>40000000</v>
-      </c>
-      <c r="AR3" s="39">
-        <v>5000000</v>
       </c>
       <c r="AS3" s="39">
         <v>5000000</v>
       </c>
       <c r="AT3" s="39">
+        <v>5000000</v>
+      </c>
+      <c r="AU3" s="39">
         <v>200000</v>
       </c>
-      <c r="AU3" s="69" t="s">
+      <c r="AV3" s="69" t="s">
         <v>70</v>
       </c>
-      <c r="AV3" s="39"/>
+      <c r="AW3" s="39"/>
     </row>
-    <row r="4" spans="1:53" s="1" customFormat="1" ht="14" customHeight="1" outlineLevel="1">
-      <c r="A4" s="46" t="s">
+    <row r="4" spans="1:54" s="1" customFormat="1" ht="14" customHeight="1" outlineLevel="1">
+      <c r="A4" s="70">
+        <v>3</v>
+      </c>
+      <c r="B4" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="34" t="s">
+      <c r="C4" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="C4" s="35" t="s">
+      <c r="D4" s="35" t="s">
         <v>65</v>
       </c>
-      <c r="D4" s="36" t="s">
+      <c r="E4" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="E4" s="36" t="s">
+      <c r="F4" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="F4" s="26">
+      <c r="G4" s="26">
         <v>7820000</v>
       </c>
-      <c r="G4" s="25">
+      <c r="H4" s="25">
         <v>1</v>
       </c>
-      <c r="H4" s="37">
+      <c r="I4" s="37">
         <v>24</v>
       </c>
-      <c r="I4" s="37">
-        <v>0</v>
-      </c>
       <c r="J4" s="37">
         <v>0</v>
       </c>
@@ -5816,94 +5838,97 @@
       <c r="P4" s="37">
         <v>0</v>
       </c>
-      <c r="Q4" s="37"/>
-      <c r="R4" s="37">
+      <c r="Q4" s="37">
+        <v>0</v>
+      </c>
+      <c r="R4" s="37"/>
+      <c r="S4" s="37">
         <v>2</v>
       </c>
-      <c r="S4" s="37">
-        <v>0</v>
-      </c>
       <c r="T4" s="37">
         <v>0</v>
       </c>
       <c r="U4" s="37">
         <v>0</v>
       </c>
-      <c r="V4" s="26"/>
+      <c r="V4" s="37">
+        <v>0</v>
+      </c>
       <c r="W4" s="26"/>
       <c r="X4" s="26"/>
       <c r="Y4" s="26"/>
-      <c r="Z4" s="26">
+      <c r="Z4" s="26"/>
+      <c r="AA4" s="26">
         <v>560000</v>
       </c>
-      <c r="AA4" s="26"/>
       <c r="AB4" s="26"/>
       <c r="AC4" s="26"/>
       <c r="AD4" s="26"/>
-      <c r="AE4" s="38"/>
+      <c r="AE4" s="26"/>
       <c r="AF4" s="38"/>
       <c r="AG4" s="38"/>
-      <c r="AH4" s="38">
+      <c r="AH4" s="38"/>
+      <c r="AI4" s="38">
         <v>6200000</v>
       </c>
-      <c r="AI4" s="38"/>
       <c r="AJ4" s="38"/>
-      <c r="AK4" s="38">
-        <v>0</v>
-      </c>
-      <c r="AL4" s="38"/>
+      <c r="AK4" s="38"/>
+      <c r="AL4" s="38">
+        <v>0</v>
+      </c>
       <c r="AM4" s="38"/>
       <c r="AN4" s="38"/>
       <c r="AO4" s="38"/>
-      <c r="AP4" s="51"/>
-      <c r="AQ4" s="40">
+      <c r="AP4" s="38"/>
+      <c r="AQ4" s="51"/>
+      <c r="AR4" s="40">
         <v>40000000</v>
       </c>
-      <c r="AR4" s="39">
-        <v>0</v>
-      </c>
       <c r="AS4" s="39">
         <v>0</v>
       </c>
       <c r="AT4" s="39">
+        <v>0</v>
+      </c>
+      <c r="AU4" s="39">
         <v>200000</v>
       </c>
-      <c r="AU4" s="69" t="s">
+      <c r="AV4" s="69" t="s">
         <v>54</v>
       </c>
-      <c r="AV4" s="39"/>
+      <c r="AW4" s="39"/>
     </row>
-    <row r="5" spans="1:53" s="28" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A5" s="33">
+    <row r="5" spans="1:54" s="28" customFormat="1" ht="19.25" customHeight="1">
+      <c r="A5" s="70">
+        <v>4</v>
+      </c>
+      <c r="B5" s="33">
         <v>2406198</v>
       </c>
-      <c r="B5" s="34" t="s">
+      <c r="C5" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="C5" s="35" t="s">
+      <c r="D5" s="35" t="s">
         <v>63</v>
       </c>
-      <c r="D5" s="36" t="s">
+      <c r="E5" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="E5" s="36" t="s">
+      <c r="F5" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="F5" s="26">
+      <c r="G5" s="26">
         <v>6990000</v>
       </c>
-      <c r="G5" s="25">
+      <c r="H5" s="25">
         <v>1</v>
       </c>
-      <c r="H5" s="37">
+      <c r="I5" s="37">
         <v>23</v>
       </c>
-      <c r="I5" s="37">
+      <c r="J5" s="37">
         <v>3</v>
       </c>
-      <c r="J5" s="37">
-        <v>0</v>
-      </c>
       <c r="K5" s="37">
         <v>0</v>
       </c>
@@ -5922,10 +5947,10 @@
       <c r="P5" s="37">
         <v>0</v>
       </c>
-      <c r="Q5" s="37"/>
-      <c r="R5" s="37">
-        <v>0</v>
-      </c>
+      <c r="Q5" s="37">
+        <v>0</v>
+      </c>
+      <c r="R5" s="37"/>
       <c r="S5" s="37">
         <v>0</v>
       </c>
@@ -5935,88 +5960,91 @@
       <c r="U5" s="37">
         <v>0</v>
       </c>
-      <c r="V5" s="26"/>
+      <c r="V5" s="37">
+        <v>0</v>
+      </c>
       <c r="W5" s="26"/>
       <c r="X5" s="26"/>
       <c r="Y5" s="26"/>
-      <c r="Z5" s="26">
+      <c r="Z5" s="26"/>
+      <c r="AA5" s="26">
         <v>720000</v>
       </c>
-      <c r="AA5" s="26"/>
       <c r="AB5" s="26"/>
       <c r="AC5" s="26"/>
       <c r="AD5" s="26"/>
-      <c r="AE5" s="38"/>
+      <c r="AE5" s="26"/>
       <c r="AF5" s="38"/>
       <c r="AG5" s="38"/>
-      <c r="AH5" s="38">
+      <c r="AH5" s="38"/>
+      <c r="AI5" s="38">
         <v>6200000</v>
       </c>
-      <c r="AI5" s="38"/>
       <c r="AJ5" s="38"/>
-      <c r="AK5" s="38">
-        <v>0</v>
-      </c>
-      <c r="AL5" s="38"/>
+      <c r="AK5" s="38"/>
+      <c r="AL5" s="38">
+        <v>0</v>
+      </c>
       <c r="AM5" s="38"/>
       <c r="AN5" s="38"/>
       <c r="AO5" s="38"/>
-      <c r="AP5" s="51"/>
-      <c r="AQ5" s="40">
+      <c r="AP5" s="38"/>
+      <c r="AQ5" s="51"/>
+      <c r="AR5" s="40">
         <v>23000000</v>
       </c>
-      <c r="AR5" s="39">
-        <v>0</v>
-      </c>
       <c r="AS5" s="39">
+        <v>0</v>
+      </c>
+      <c r="AT5" s="39">
         <v>2000000</v>
       </c>
-      <c r="AT5" s="39">
+      <c r="AU5" s="39">
         <v>200000</v>
       </c>
-      <c r="AU5" s="69" t="s">
+      <c r="AV5" s="69" t="s">
         <v>70</v>
       </c>
-      <c r="AV5" s="39"/>
-      <c r="AZ5" s="29"/>
-      <c r="BA5" s="30"/>
+      <c r="AW5" s="39"/>
+      <c r="BA5" s="29"/>
+      <c r="BB5" s="30"/>
     </row>
-    <row r="6" spans="1:53" s="28" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A6" s="46" t="s">
+    <row r="6" spans="1:54" s="28" customFormat="1" ht="19.25" customHeight="1">
+      <c r="A6" s="70">
+        <v>5</v>
+      </c>
+      <c r="B6" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="34" t="s">
+      <c r="C6" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="C6" s="35" t="s">
+      <c r="D6" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="D6" s="36" t="s">
+      <c r="E6" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="E6" s="36" t="s">
+      <c r="F6" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="F6" s="26">
+      <c r="G6" s="26">
         <v>4850000</v>
       </c>
-      <c r="G6" s="25">
+      <c r="H6" s="25">
         <v>1</v>
       </c>
-      <c r="H6" s="37">
+      <c r="I6" s="37">
         <v>22</v>
       </c>
-      <c r="I6" s="37">
-        <v>0</v>
-      </c>
       <c r="J6" s="37">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K6" s="37">
         <v>2</v>
       </c>
       <c r="L6" s="37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6" s="37">
         <v>0</v>
@@ -6028,12 +6056,12 @@
         <v>0</v>
       </c>
       <c r="P6" s="37">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="37">
         <v>2</v>
       </c>
-      <c r="Q6" s="37"/>
-      <c r="R6" s="37">
-        <v>0</v>
-      </c>
+      <c r="R6" s="37"/>
       <c r="S6" s="37">
         <v>0</v>
       </c>
@@ -6043,80 +6071,83 @@
       <c r="U6" s="37">
         <v>0</v>
       </c>
-      <c r="V6" s="26"/>
+      <c r="V6" s="37">
+        <v>0</v>
+      </c>
       <c r="W6" s="26"/>
       <c r="X6" s="26"/>
       <c r="Y6" s="26"/>
-      <c r="Z6" s="26">
+      <c r="Z6" s="26"/>
+      <c r="AA6" s="26">
         <v>560000</v>
       </c>
-      <c r="AA6" s="26"/>
       <c r="AB6" s="26"/>
       <c r="AC6" s="26"/>
       <c r="AD6" s="26"/>
-      <c r="AE6" s="38"/>
+      <c r="AE6" s="26"/>
       <c r="AF6" s="38"/>
       <c r="AG6" s="38"/>
-      <c r="AH6" s="38">
+      <c r="AH6" s="38"/>
+      <c r="AI6" s="38">
         <v>6200000</v>
       </c>
-      <c r="AI6" s="38"/>
       <c r="AJ6" s="38"/>
-      <c r="AK6" s="38">
-        <v>0</v>
-      </c>
-      <c r="AL6" s="38"/>
+      <c r="AK6" s="38"/>
+      <c r="AL6" s="38">
+        <v>0</v>
+      </c>
       <c r="AM6" s="38"/>
       <c r="AN6" s="38"/>
       <c r="AO6" s="38"/>
-      <c r="AP6" s="51"/>
-      <c r="AQ6" s="40">
+      <c r="AP6" s="38"/>
+      <c r="AQ6" s="51"/>
+      <c r="AR6" s="40">
         <v>11000000</v>
       </c>
-      <c r="AR6" s="39">
-        <v>0</v>
-      </c>
       <c r="AS6" s="39">
         <v>0</v>
       </c>
       <c r="AT6" s="39">
+        <v>0</v>
+      </c>
+      <c r="AU6" s="39">
         <v>200000</v>
       </c>
-      <c r="AU6" s="69" t="s">
+      <c r="AV6" s="69" t="s">
         <v>54</v>
       </c>
-      <c r="AV6" s="39"/>
-      <c r="AZ6" s="29"/>
-      <c r="BA6" s="30"/>
+      <c r="AW6" s="39"/>
+      <c r="BA6" s="29"/>
+      <c r="BB6" s="30"/>
     </row>
-    <row r="7" spans="1:53" s="31" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A7" s="33">
+    <row r="7" spans="1:54" s="31" customFormat="1" ht="19.25" customHeight="1">
+      <c r="A7" s="70">
+        <v>6</v>
+      </c>
+      <c r="B7" s="33">
         <v>2406145</v>
       </c>
-      <c r="B7" s="34" t="s">
+      <c r="C7" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="C7" s="35" t="s">
+      <c r="D7" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="D7" s="36" t="s">
+      <c r="E7" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="36" t="s">
+      <c r="F7" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="F7" s="26">
+      <c r="G7" s="26">
         <v>6340000</v>
       </c>
-      <c r="G7" s="25">
+      <c r="H7" s="25">
         <v>1</v>
       </c>
-      <c r="H7" s="37">
+      <c r="I7" s="37">
         <v>26</v>
       </c>
-      <c r="I7" s="37">
-        <v>0</v>
-      </c>
       <c r="J7" s="37">
         <v>0</v>
       </c>
@@ -6138,10 +6169,10 @@
       <c r="P7" s="37">
         <v>0</v>
       </c>
-      <c r="Q7" s="37"/>
-      <c r="R7" s="37">
-        <v>0</v>
-      </c>
+      <c r="Q7" s="37">
+        <v>0</v>
+      </c>
+      <c r="R7" s="37"/>
       <c r="S7" s="37">
         <v>0</v>
       </c>
@@ -6151,80 +6182,83 @@
       <c r="U7" s="37">
         <v>0</v>
       </c>
-      <c r="V7" s="26"/>
+      <c r="V7" s="37">
+        <v>0</v>
+      </c>
       <c r="W7" s="26"/>
       <c r="X7" s="26"/>
       <c r="Y7" s="26"/>
-      <c r="Z7" s="26">
+      <c r="Z7" s="26"/>
+      <c r="AA7" s="26">
         <v>720000</v>
       </c>
-      <c r="AA7" s="26"/>
       <c r="AB7" s="26"/>
       <c r="AC7" s="26"/>
       <c r="AD7" s="26"/>
-      <c r="AE7" s="38"/>
+      <c r="AE7" s="26"/>
       <c r="AF7" s="38"/>
       <c r="AG7" s="38"/>
-      <c r="AH7" s="38">
+      <c r="AH7" s="38"/>
+      <c r="AI7" s="38">
         <v>6200000</v>
       </c>
-      <c r="AI7" s="38"/>
       <c r="AJ7" s="38"/>
-      <c r="AK7" s="38">
-        <v>0</v>
-      </c>
-      <c r="AL7" s="38"/>
+      <c r="AK7" s="38"/>
+      <c r="AL7" s="38">
+        <v>0</v>
+      </c>
       <c r="AM7" s="38"/>
       <c r="AN7" s="38"/>
       <c r="AO7" s="38"/>
-      <c r="AP7" s="51"/>
-      <c r="AQ7" s="40">
+      <c r="AP7" s="38"/>
+      <c r="AQ7" s="51"/>
+      <c r="AR7" s="40">
         <v>23000000</v>
       </c>
-      <c r="AR7" s="39">
-        <v>0</v>
-      </c>
       <c r="AS7" s="39">
         <v>0</v>
       </c>
       <c r="AT7" s="39">
+        <v>0</v>
+      </c>
+      <c r="AU7" s="39">
         <v>200000</v>
       </c>
-      <c r="AU7" s="69" t="s">
+      <c r="AV7" s="69" t="s">
         <v>70</v>
       </c>
-      <c r="AV7" s="39"/>
-      <c r="AZ7" s="29"/>
-      <c r="BA7" s="30"/>
+      <c r="AW7" s="39"/>
+      <c r="BA7" s="29"/>
+      <c r="BB7" s="30"/>
     </row>
-    <row r="8" spans="1:53" s="31" customFormat="1" ht="38.25" customHeight="1">
-      <c r="A8" s="46" t="s">
+    <row r="8" spans="1:54" s="31" customFormat="1" ht="38.25" customHeight="1">
+      <c r="A8" s="70">
+        <v>7</v>
+      </c>
+      <c r="B8" s="46" t="s">
         <v>53</v>
       </c>
-      <c r="B8" s="34" t="s">
+      <c r="C8" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="C8" s="35" t="s">
+      <c r="D8" s="35" t="s">
         <v>67</v>
       </c>
-      <c r="D8" s="36" t="s">
+      <c r="E8" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="E8" s="36" t="s">
+      <c r="F8" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="F8" s="26">
+      <c r="G8" s="26">
         <v>9000010</v>
       </c>
-      <c r="G8" s="25">
+      <c r="H8" s="25">
         <v>1</v>
       </c>
-      <c r="H8" s="37">
+      <c r="I8" s="37">
         <v>26</v>
       </c>
-      <c r="I8" s="37">
-        <v>0</v>
-      </c>
       <c r="J8" s="37">
         <v>0</v>
       </c>
@@ -6235,21 +6269,21 @@
         <v>0</v>
       </c>
       <c r="M8" s="37">
+        <v>0</v>
+      </c>
+      <c r="N8" s="37">
         <v>5</v>
       </c>
-      <c r="N8" s="37">
+      <c r="O8" s="37">
         <v>2</v>
       </c>
-      <c r="O8" s="37">
-        <v>0</v>
-      </c>
       <c r="P8" s="37">
         <v>0</v>
       </c>
-      <c r="Q8" s="37"/>
-      <c r="R8" s="37">
-        <v>0</v>
-      </c>
+      <c r="Q8" s="37">
+        <v>0</v>
+      </c>
+      <c r="R8" s="37"/>
       <c r="S8" s="37">
         <v>0</v>
       </c>
@@ -6259,63 +6293,65 @@
       <c r="U8" s="37">
         <v>0</v>
       </c>
-      <c r="V8" s="26"/>
+      <c r="V8" s="37">
+        <v>0</v>
+      </c>
       <c r="W8" s="26"/>
       <c r="X8" s="26"/>
       <c r="Y8" s="26"/>
-      <c r="Z8" s="26">
+      <c r="Z8" s="26"/>
+      <c r="AA8" s="26">
         <v>560000</v>
       </c>
-      <c r="AA8" s="26"/>
       <c r="AB8" s="26"/>
       <c r="AC8" s="26"/>
       <c r="AD8" s="26"/>
-      <c r="AE8" s="38"/>
+      <c r="AE8" s="26"/>
       <c r="AF8" s="38"/>
       <c r="AG8" s="38"/>
-      <c r="AH8" s="38">
+      <c r="AH8" s="38"/>
+      <c r="AI8" s="38">
         <v>6200000</v>
       </c>
-      <c r="AI8" s="38"/>
       <c r="AJ8" s="38"/>
-      <c r="AK8" s="38">
-        <v>0</v>
-      </c>
-      <c r="AL8" s="38"/>
+      <c r="AK8" s="38"/>
+      <c r="AL8" s="38">
+        <v>0</v>
+      </c>
       <c r="AM8" s="38"/>
       <c r="AN8" s="38"/>
       <c r="AO8" s="38"/>
-      <c r="AP8" s="51"/>
-      <c r="AQ8" s="40">
+      <c r="AP8" s="38"/>
+      <c r="AQ8" s="51"/>
+      <c r="AR8" s="40">
         <v>17000000</v>
       </c>
-      <c r="AR8" s="39">
-        <v>0</v>
-      </c>
       <c r="AS8" s="39">
         <v>0</v>
       </c>
       <c r="AT8" s="39">
+        <v>0</v>
+      </c>
+      <c r="AU8" s="39">
         <v>200000</v>
       </c>
-      <c r="AU8" s="69" t="s">
+      <c r="AV8" s="69" t="s">
         <v>54</v>
       </c>
-      <c r="AV8" s="39"/>
-      <c r="AW8" s="28"/>
-      <c r="AX8" s="32"/>
-      <c r="AZ8" s="29"/>
-      <c r="BA8" s="30"/>
+      <c r="AW8" s="39"/>
+      <c r="AX8" s="28"/>
+      <c r="AY8" s="32"/>
+      <c r="BA8" s="29"/>
+      <c r="BB8" s="30"/>
     </row>
-    <row r="9" spans="1:53" s="45" customFormat="1" ht="19">
-      <c r="A9" s="3"/>
-      <c r="B9" s="2"/>
+    <row r="9" spans="1:54" s="45" customFormat="1" ht="19">
+      <c r="B9" s="3"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="5"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="4"/>
       <c r="I9" s="5"/>
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
@@ -6325,11 +6361,11 @@
       <c r="O9" s="5"/>
       <c r="P9" s="5"/>
       <c r="Q9" s="5"/>
-      <c r="R9" s="6"/>
+      <c r="R9" s="5"/>
       <c r="S9" s="6"/>
-      <c r="T9" s="7"/>
+      <c r="T9" s="6"/>
       <c r="U9" s="7"/>
-      <c r="V9" s="8"/>
+      <c r="V9" s="7"/>
       <c r="W9" s="8"/>
       <c r="X9" s="8"/>
       <c r="Y9" s="8"/>
@@ -6338,110 +6374,110 @@
       <c r="AB9" s="8"/>
       <c r="AC9" s="8"/>
       <c r="AD9" s="8"/>
-      <c r="AE9" s="2"/>
+      <c r="AE9" s="8"/>
       <c r="AF9" s="2"/>
       <c r="AG9" s="2"/>
       <c r="AH9" s="2"/>
       <c r="AI9" s="2"/>
       <c r="AJ9" s="2"/>
       <c r="AK9" s="2"/>
-      <c r="AL9" s="9"/>
+      <c r="AL9" s="2"/>
       <c r="AM9" s="9"/>
       <c r="AN9" s="9"/>
       <c r="AO9" s="9"/>
       <c r="AP9" s="9"/>
-      <c r="AQ9" s="11"/>
+      <c r="AQ9" s="9"/>
       <c r="AR9" s="11"/>
       <c r="AS9" s="11"/>
       <c r="AT9" s="11"/>
-      <c r="AU9" s="27"/>
+      <c r="AU9" s="11"/>
       <c r="AV9" s="27"/>
-      <c r="AW9" s="41"/>
-      <c r="AX9" s="42"/>
+      <c r="AW9" s="27"/>
+      <c r="AX9" s="41"/>
       <c r="AY9" s="42"/>
-      <c r="AZ9" s="43"/>
-      <c r="BA9" s="44"/>
+      <c r="AZ9" s="42"/>
+      <c r="BA9" s="43"/>
+      <c r="BB9" s="44"/>
     </row>
-    <row r="10" spans="1:53" s="45" customFormat="1" ht="21">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
+    <row r="10" spans="1:54" s="45" customFormat="1" ht="21">
+      <c r="B10" s="13"/>
       <c r="C10" s="14"/>
       <c r="D10" s="14"/>
       <c r="E10" s="14"/>
       <c r="F10" s="14"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="16"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="15"/>
       <c r="I10" s="16"/>
       <c r="J10" s="16"/>
       <c r="K10" s="16"/>
       <c r="L10" s="16"/>
       <c r="M10" s="16"/>
       <c r="N10" s="16"/>
-      <c r="O10" s="12"/>
+      <c r="O10" s="16"/>
       <c r="P10" s="12"/>
       <c r="Q10" s="12"/>
-      <c r="R10" s="18"/>
-      <c r="S10" s="16"/>
-      <c r="T10" s="14"/>
+      <c r="R10" s="12"/>
+      <c r="S10" s="18"/>
+      <c r="T10" s="16"/>
       <c r="U10" s="14"/>
-      <c r="V10" s="19"/>
+      <c r="V10" s="14"/>
       <c r="W10" s="19"/>
-      <c r="X10" s="14"/>
+      <c r="X10" s="19"/>
       <c r="Y10" s="14"/>
       <c r="Z10" s="14"/>
       <c r="AA10" s="14"/>
       <c r="AB10" s="14"/>
       <c r="AC10" s="14"/>
       <c r="AD10" s="14"/>
-      <c r="AE10" s="20"/>
+      <c r="AE10" s="14"/>
       <c r="AF10" s="20"/>
-      <c r="AG10" s="12"/>
+      <c r="AG10" s="20"/>
       <c r="AH10" s="12"/>
       <c r="AI10" s="12"/>
-      <c r="AJ10" s="14"/>
+      <c r="AJ10" s="12"/>
       <c r="AK10" s="14"/>
-      <c r="AL10" s="14" t="s">
+      <c r="AL10" s="14"/>
+      <c r="AM10" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="AM10" s="14"/>
       <c r="AN10" s="14"/>
       <c r="AO10" s="14"/>
       <c r="AP10" s="14"/>
-      <c r="AQ10" s="22"/>
+      <c r="AQ10" s="14"/>
       <c r="AR10" s="22"/>
       <c r="AS10" s="22"/>
       <c r="AT10" s="22"/>
-      <c r="AU10" s="12"/>
-      <c r="AV10" s="20"/>
-      <c r="AW10" s="41"/>
-      <c r="AX10" s="42"/>
+      <c r="AU10" s="22"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="20"/>
+      <c r="AX10" s="41"/>
       <c r="AY10" s="42"/>
-      <c r="AZ10" s="43"/>
-      <c r="BA10" s="44"/>
+      <c r="AZ10" s="42"/>
+      <c r="BA10" s="43"/>
+      <c r="BB10" s="44"/>
     </row>
-    <row r="11" spans="1:53" s="45" customFormat="1" ht="21">
-      <c r="A11" s="23"/>
-      <c r="B11" s="12"/>
+    <row r="11" spans="1:54" s="45" customFormat="1" ht="21">
+      <c r="B11" s="23"/>
       <c r="C11" s="12"/>
       <c r="D11" s="12"/>
       <c r="E11" s="12"/>
       <c r="F11" s="12"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="18"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="15"/>
       <c r="I11" s="18"/>
       <c r="J11" s="18"/>
       <c r="K11" s="18"/>
       <c r="L11" s="18"/>
       <c r="M11" s="18"/>
       <c r="N11" s="18"/>
-      <c r="O11" s="17"/>
-      <c r="P11" s="12"/>
+      <c r="O11" s="18"/>
+      <c r="P11" s="17"/>
       <c r="Q11" s="12"/>
-      <c r="R11" s="18"/>
+      <c r="R11" s="12"/>
       <c r="S11" s="18"/>
-      <c r="T11" s="24"/>
+      <c r="T11" s="18"/>
       <c r="U11" s="24"/>
-      <c r="V11" s="19"/>
+      <c r="V11" s="24"/>
       <c r="W11" s="19"/>
       <c r="X11" s="19"/>
       <c r="Y11" s="19"/>
@@ -6449,40 +6485,40 @@
       <c r="AA11" s="19"/>
       <c r="AB11" s="19"/>
       <c r="AC11" s="19"/>
-      <c r="AD11" s="14"/>
-      <c r="AE11" s="12"/>
+      <c r="AD11" s="19"/>
+      <c r="AE11" s="14"/>
       <c r="AF11" s="12"/>
       <c r="AG11" s="12"/>
       <c r="AH11" s="12"/>
       <c r="AI11" s="12"/>
-      <c r="AJ11" s="14"/>
-      <c r="AK11" s="20"/>
-      <c r="AL11" s="12"/>
+      <c r="AJ11" s="12"/>
+      <c r="AK11" s="14"/>
+      <c r="AL11" s="20"/>
       <c r="AM11" s="12"/>
       <c r="AN11" s="12"/>
       <c r="AO11" s="12"/>
       <c r="AP11" s="12"/>
-      <c r="AQ11" s="22"/>
+      <c r="AQ11" s="12"/>
       <c r="AR11" s="22"/>
       <c r="AS11" s="22"/>
       <c r="AT11" s="22"/>
-      <c r="AU11" s="12"/>
+      <c r="AU11" s="22"/>
       <c r="AV11" s="12"/>
-      <c r="AW11" s="41"/>
-      <c r="AX11" s="42"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="41"/>
       <c r="AY11" s="42"/>
-      <c r="AZ11" s="43"/>
-      <c r="BA11" s="44"/>
+      <c r="AZ11" s="42"/>
+      <c r="BA11" s="43"/>
+      <c r="BB11" s="44"/>
     </row>
-    <row r="12" spans="1:53" s="45" customFormat="1" ht="20">
-      <c r="A12" s="47"/>
-      <c r="B12" s="48"/>
-      <c r="C12" s="49"/>
+    <row r="12" spans="1:54" s="45" customFormat="1" ht="20">
+      <c r="B12" s="47"/>
+      <c r="C12" s="48"/>
       <c r="D12" s="49"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="51"/>
-      <c r="G12" s="52"/>
-      <c r="H12" s="53"/>
+      <c r="E12" s="49"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="51"/>
+      <c r="H12" s="52"/>
       <c r="I12" s="53"/>
       <c r="J12" s="53"/>
       <c r="K12" s="53"/>
@@ -6496,7 +6532,7 @@
       <c r="S12" s="53"/>
       <c r="T12" s="53"/>
       <c r="U12" s="53"/>
-      <c r="V12" s="51"/>
+      <c r="V12" s="53"/>
       <c r="W12" s="51"/>
       <c r="X12" s="51"/>
       <c r="Y12" s="51"/>
@@ -6521,23 +6557,23 @@
       <c r="AR12" s="51"/>
       <c r="AS12" s="51"/>
       <c r="AT12" s="51"/>
-      <c r="AU12" s="54"/>
+      <c r="AU12" s="51"/>
       <c r="AV12" s="54"/>
-      <c r="AW12" s="41"/>
-      <c r="AX12" s="42"/>
+      <c r="AW12" s="54"/>
+      <c r="AX12" s="41"/>
       <c r="AY12" s="42"/>
-      <c r="AZ12" s="43"/>
-      <c r="BA12" s="44"/>
+      <c r="AZ12" s="42"/>
+      <c r="BA12" s="43"/>
+      <c r="BB12" s="44"/>
     </row>
-    <row r="13" spans="1:53" s="45" customFormat="1">
-      <c r="A13" s="47"/>
-      <c r="B13" s="56"/>
-      <c r="C13" s="49"/>
+    <row r="13" spans="1:54" s="45" customFormat="1">
+      <c r="B13" s="47"/>
+      <c r="C13" s="56"/>
       <c r="D13" s="49"/>
-      <c r="E13" s="50"/>
-      <c r="F13" s="51"/>
-      <c r="G13" s="52"/>
-      <c r="H13" s="53"/>
+      <c r="E13" s="49"/>
+      <c r="F13" s="50"/>
+      <c r="G13" s="51"/>
+      <c r="H13" s="52"/>
       <c r="I13" s="53"/>
       <c r="J13" s="53"/>
       <c r="K13" s="53"/>
@@ -6551,7 +6587,7 @@
       <c r="S13" s="53"/>
       <c r="T13" s="53"/>
       <c r="U13" s="53"/>
-      <c r="V13" s="51"/>
+      <c r="V13" s="53"/>
       <c r="W13" s="51"/>
       <c r="X13" s="51"/>
       <c r="Y13" s="51"/>
@@ -6576,23 +6612,23 @@
       <c r="AR13" s="51"/>
       <c r="AS13" s="51"/>
       <c r="AT13" s="51"/>
-      <c r="AU13" s="54"/>
+      <c r="AU13" s="51"/>
       <c r="AV13" s="54"/>
-      <c r="AW13" s="41"/>
-      <c r="AX13" s="42"/>
+      <c r="AW13" s="54"/>
+      <c r="AX13" s="41"/>
       <c r="AY13" s="42"/>
-      <c r="AZ13" s="43"/>
-      <c r="BA13" s="44"/>
+      <c r="AZ13" s="42"/>
+      <c r="BA13" s="43"/>
+      <c r="BB13" s="44"/>
     </row>
-    <row r="14" spans="1:53" s="45" customFormat="1">
-      <c r="A14" s="47"/>
-      <c r="B14" s="56"/>
-      <c r="C14" s="49"/>
+    <row r="14" spans="1:54" s="45" customFormat="1">
+      <c r="B14" s="47"/>
+      <c r="C14" s="56"/>
       <c r="D14" s="49"/>
-      <c r="E14" s="50"/>
-      <c r="F14" s="51"/>
-      <c r="G14" s="52"/>
-      <c r="H14" s="53"/>
+      <c r="E14" s="49"/>
+      <c r="F14" s="50"/>
+      <c r="G14" s="51"/>
+      <c r="H14" s="52"/>
       <c r="I14" s="53"/>
       <c r="J14" s="53"/>
       <c r="K14" s="53"/>
@@ -6606,7 +6642,7 @@
       <c r="S14" s="53"/>
       <c r="T14" s="53"/>
       <c r="U14" s="53"/>
-      <c r="V14" s="51"/>
+      <c r="V14" s="53"/>
       <c r="W14" s="51"/>
       <c r="X14" s="51"/>
       <c r="Y14" s="51"/>
@@ -6631,23 +6667,23 @@
       <c r="AR14" s="51"/>
       <c r="AS14" s="51"/>
       <c r="AT14" s="51"/>
-      <c r="AU14" s="54"/>
+      <c r="AU14" s="51"/>
       <c r="AV14" s="54"/>
-      <c r="AW14" s="41"/>
-      <c r="AX14" s="42"/>
+      <c r="AW14" s="54"/>
+      <c r="AX14" s="41"/>
       <c r="AY14" s="42"/>
-      <c r="AZ14" s="43"/>
-      <c r="BA14" s="44"/>
+      <c r="AZ14" s="42"/>
+      <c r="BA14" s="43"/>
+      <c r="BB14" s="44"/>
     </row>
-    <row r="15" spans="1:53" s="45" customFormat="1">
-      <c r="A15" s="47"/>
-      <c r="B15" s="56"/>
-      <c r="C15" s="49"/>
+    <row r="15" spans="1:54" s="45" customFormat="1">
+      <c r="B15" s="47"/>
+      <c r="C15" s="56"/>
       <c r="D15" s="49"/>
-      <c r="E15" s="50"/>
-      <c r="F15" s="51"/>
-      <c r="G15" s="52"/>
-      <c r="H15" s="53"/>
+      <c r="E15" s="49"/>
+      <c r="F15" s="50"/>
+      <c r="G15" s="51"/>
+      <c r="H15" s="52"/>
       <c r="I15" s="53"/>
       <c r="J15" s="53"/>
       <c r="K15" s="53"/>
@@ -6661,7 +6697,7 @@
       <c r="S15" s="53"/>
       <c r="T15" s="53"/>
       <c r="U15" s="53"/>
-      <c r="V15" s="51"/>
+      <c r="V15" s="53"/>
       <c r="W15" s="51"/>
       <c r="X15" s="51"/>
       <c r="Y15" s="51"/>
@@ -6686,23 +6722,23 @@
       <c r="AR15" s="51"/>
       <c r="AS15" s="51"/>
       <c r="AT15" s="51"/>
-      <c r="AU15" s="54"/>
+      <c r="AU15" s="51"/>
       <c r="AV15" s="54"/>
-      <c r="AW15" s="41"/>
-      <c r="AX15" s="42"/>
+      <c r="AW15" s="54"/>
+      <c r="AX15" s="41"/>
       <c r="AY15" s="42"/>
-      <c r="AZ15" s="43"/>
-      <c r="BA15" s="44"/>
+      <c r="AZ15" s="42"/>
+      <c r="BA15" s="43"/>
+      <c r="BB15" s="44"/>
     </row>
-    <row r="16" spans="1:53" s="2" customFormat="1" ht="18">
-      <c r="A16" s="47"/>
-      <c r="B16" s="56"/>
-      <c r="C16" s="49"/>
+    <row r="16" spans="1:54" s="2" customFormat="1" ht="18">
+      <c r="B16" s="47"/>
+      <c r="C16" s="56"/>
       <c r="D16" s="49"/>
-      <c r="E16" s="50"/>
-      <c r="F16" s="51"/>
-      <c r="G16" s="52"/>
-      <c r="H16" s="53"/>
+      <c r="E16" s="49"/>
+      <c r="F16" s="50"/>
+      <c r="G16" s="51"/>
+      <c r="H16" s="52"/>
       <c r="I16" s="53"/>
       <c r="J16" s="53"/>
       <c r="K16" s="53"/>
@@ -6716,7 +6752,7 @@
       <c r="S16" s="53"/>
       <c r="T16" s="53"/>
       <c r="U16" s="53"/>
-      <c r="V16" s="51"/>
+      <c r="V16" s="53"/>
       <c r="W16" s="51"/>
       <c r="X16" s="51"/>
       <c r="Y16" s="51"/>
@@ -6741,19 +6777,19 @@
       <c r="AR16" s="51"/>
       <c r="AS16" s="51"/>
       <c r="AT16" s="51"/>
-      <c r="AU16" s="54"/>
+      <c r="AU16" s="51"/>
       <c r="AV16" s="54"/>
-      <c r="AX16" s="10"/>
+      <c r="AW16" s="54"/>
+      <c r="AY16" s="10"/>
     </row>
-    <row r="17" spans="1:50" s="12" customFormat="1" ht="20">
-      <c r="A17" s="47"/>
-      <c r="B17" s="56"/>
-      <c r="C17" s="49"/>
+    <row r="17" spans="2:51" s="12" customFormat="1" ht="20">
+      <c r="B17" s="47"/>
+      <c r="C17" s="56"/>
       <c r="D17" s="49"/>
-      <c r="E17" s="50"/>
-      <c r="F17" s="51"/>
-      <c r="G17" s="52"/>
-      <c r="H17" s="53"/>
+      <c r="E17" s="49"/>
+      <c r="F17" s="50"/>
+      <c r="G17" s="51"/>
+      <c r="H17" s="52"/>
       <c r="I17" s="53"/>
       <c r="J17" s="53"/>
       <c r="K17" s="53"/>
@@ -6767,7 +6803,7 @@
       <c r="S17" s="53"/>
       <c r="T17" s="53"/>
       <c r="U17" s="53"/>
-      <c r="V17" s="51"/>
+      <c r="V17" s="53"/>
       <c r="W17" s="51"/>
       <c r="X17" s="51"/>
       <c r="Y17" s="51"/>
@@ -6792,18 +6828,18 @@
       <c r="AR17" s="51"/>
       <c r="AS17" s="51"/>
       <c r="AT17" s="51"/>
-      <c r="AU17" s="54"/>
+      <c r="AU17" s="51"/>
       <c r="AV17" s="54"/>
+      <c r="AW17" s="54"/>
     </row>
-    <row r="18" spans="1:50" s="12" customFormat="1" ht="20">
-      <c r="A18" s="47"/>
-      <c r="B18" s="56"/>
-      <c r="C18" s="49"/>
+    <row r="18" spans="2:51" s="12" customFormat="1" ht="20">
+      <c r="B18" s="47"/>
+      <c r="C18" s="56"/>
       <c r="D18" s="49"/>
-      <c r="E18" s="50"/>
-      <c r="F18" s="51"/>
-      <c r="G18" s="52"/>
-      <c r="H18" s="53"/>
+      <c r="E18" s="49"/>
+      <c r="F18" s="50"/>
+      <c r="G18" s="51"/>
+      <c r="H18" s="52"/>
       <c r="I18" s="53"/>
       <c r="J18" s="53"/>
       <c r="K18" s="53"/>
@@ -6817,7 +6853,7 @@
       <c r="S18" s="53"/>
       <c r="T18" s="53"/>
       <c r="U18" s="53"/>
-      <c r="V18" s="51"/>
+      <c r="V18" s="53"/>
       <c r="W18" s="51"/>
       <c r="X18" s="51"/>
       <c r="Y18" s="51"/>
@@ -6842,17 +6878,18 @@
       <c r="AR18" s="51"/>
       <c r="AS18" s="51"/>
       <c r="AT18" s="51"/>
-      <c r="AU18" s="54"/>
+      <c r="AU18" s="51"/>
       <c r="AV18" s="54"/>
-      <c r="AX18" s="21"/>
+      <c r="AW18" s="54"/>
+      <c r="AY18" s="21"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1">
+  <conditionalFormatting sqref="B1">
     <cfRule type="duplicateValues" dxfId="5" priority="11"/>
     <cfRule type="duplicateValues" dxfId="4" priority="12"/>
     <cfRule type="duplicateValues" dxfId="3" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A1048576">
+  <conditionalFormatting sqref="B2:B1048576">
     <cfRule type="duplicateValues" dxfId="2" priority="5"/>
     <cfRule type="duplicateValues" dxfId="1" priority="6"/>
     <cfRule type="duplicateValues" dxfId="0" priority="7"/>

--- a/thaco/color/1_DATA_AllCols.xlsx
+++ b/thaco/color/1_DATA_AllCols.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adity/Documents/GitHub/gitlocal/thaco/color/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A487890-4523-BC49-8FCE-1106C5FF6D92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED26442F-8C68-1943-8886-7D61A58E7DDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39220" yWindow="600" windowWidth="33760" windowHeight="18480" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1360" yWindow="500" windowWidth="33760" windowHeight="18480" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bảng lương CB-NV" sheetId="5" r:id="rId1"/>
@@ -4830,7 +4830,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5002,9 +5002,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
@@ -5423,7 +5420,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:54" s="68" customFormat="1" ht="54" customHeight="1" outlineLevel="1">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="71" t="s">
         <v>71</v>
       </c>
       <c r="B1" s="57" t="s">
@@ -5572,7 +5569,7 @@
       </c>
     </row>
     <row r="2" spans="1:54" s="1" customFormat="1" ht="14" customHeight="1" outlineLevel="1">
-      <c r="A2" s="71">
+      <c r="A2" s="70">
         <v>1</v>
       </c>
       <c r="B2" s="33">
@@ -5585,7 +5582,7 @@
         <v>63</v>
       </c>
       <c r="E2" s="36" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F2" s="36" t="s">
         <v>48</v>
@@ -6134,7 +6131,7 @@
         <v>64</v>
       </c>
       <c r="E7" s="36" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F7" s="36" t="s">
         <v>48</v>
